--- a/dataset_t6_grouped/results2/G4/G4_T3603_W0074F0001T0006Z000C1N34_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3603_W0074F0001T0006Z000C1N34_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>72.67810386986197</v>
+        <v>11.81019187885257</v>
       </c>
       <c r="D2" t="n">
-        <v>37.2744562025262</v>
+        <v>6.057099132910507</v>
       </c>
       <c r="E2" t="n">
-        <v>10.5079005477905</v>
+        <v>1.707533839015956</v>
       </c>
       <c r="F2" t="n">
-        <v>6.525005385482373</v>
+        <v>1.060313375140886</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>93.69390496544297</v>
+        <v>15.22525955688448</v>
       </c>
       <c r="D3" t="n">
-        <v>50.32446697349094</v>
+        <v>8.177725883192279</v>
       </c>
       <c r="E3" t="n">
-        <v>10.5079005477905</v>
+        <v>1.707533839015956</v>
       </c>
       <c r="F3" t="n">
-        <v>6.525005385482373</v>
+        <v>1.060313375140886</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
